--- a/api/data/examples/ferias.xlsx
+++ b/api/data/examples/ferias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/tabelas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/projeto-intranet/api/data/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7564D4EE-2108-6D49-A6FF-03B98EADC6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A8FA13-44FD-D64F-8AF0-54BA8C258018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{A2FF50CB-4187-0D41-A4FB-C79E75C830FA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Funcionário</t>
   </si>
@@ -48,6 +48,21 @@
   </si>
   <si>
     <t>Sandra</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>Isau</t>
+  </si>
+  <si>
+    <t>Cleide</t>
+  </si>
+  <si>
+    <t>Yuri</t>
+  </si>
+  <si>
+    <t>Marina</t>
   </si>
 </sst>
 </file>
@@ -89,10 +104,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,21 +443,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E84C4B5-53AD-9149-BC64-D5C8B1ED12AF}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -457,19 +473,59 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46160</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46174</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46174</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46193</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46146</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46195</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/api/data/examples/ferias.xlsx
+++ b/api/data/examples/ferias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/projeto-intranet/api/data/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A8FA13-44FD-D64F-8AF0-54BA8C258018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBB519E-BC7D-C447-89CC-7F636422E359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{A2FF50CB-4187-0D41-A4FB-C79E75C830FA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Funcionário</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Término das Férias</t>
   </si>
   <si>
-    <t>Sandra</t>
-  </si>
-  <si>
     <t>Andrea</t>
   </si>
   <si>
@@ -63,6 +60,87 @@
   </si>
   <si>
     <t>Marina</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>20/06/2026</t>
+  </si>
+  <si>
+    <t>22/06/2026</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>Nicolly</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>21/07/2026</t>
+  </si>
+  <si>
+    <t>Débora</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>11/08/2026</t>
+  </si>
+  <si>
+    <t>Elisa</t>
+  </si>
+  <si>
+    <t>02/08/2026</t>
+  </si>
+  <si>
+    <t>Lorena</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>Tamiris</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>Samantha</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
   </si>
 </sst>
 </file>
@@ -443,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E84C4B5-53AD-9149-BC64-D5C8B1ED12AF}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -463,68 +541,145 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46069</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46083</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
-        <v>46160</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46174</v>
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46174</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46193</v>
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46188</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46217</v>
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46146</v>
-      </c>
-      <c r="C6" s="3">
-        <v>46175</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46174</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46195</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
